--- a/family_tree_project/alto_family/excel/Alto Family Tree.xlsx
+++ b/family_tree_project/alto_family/excel/Alto Family Tree.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48fcbf0fe29d15ca/Documents/Personal/My Personal Projects/GitHub/washingtonalto.github.io/family_tree_project/alto_family/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{50D98804-C5B4-443B-9209-2A692216128A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="6_{50D98804-C5B4-443B-9209-2A692216128A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC664589-3D69-46BC-9CDF-BE29D8EB032D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9A1E33E0-BCBF-411C-B6A4-073C88D53E64}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="106">
   <si>
     <t>ALTO FAMILY DATA ENTRY</t>
   </si>
@@ -288,27 +288,15 @@
     <t>Rebecca Reyes Alto</t>
   </si>
   <si>
-    <t>Richard Obilex</t>
-  </si>
-  <si>
-    <t>Jo Ann Alto-Obilex</t>
-  </si>
-  <si>
     <t>Joel Adam Alto</t>
   </si>
   <si>
-    <t>Lea Abello Alto</t>
-  </si>
-  <si>
     <t>Jesy Angeli Alto</t>
   </si>
   <si>
     <t>Fabian Lim</t>
   </si>
   <si>
-    <t>Grace Ann Lim</t>
-  </si>
-  <si>
     <t>Jason Alto</t>
   </si>
   <si>
@@ -360,9 +348,6 @@
     <t>Dianne Joy Zano</t>
   </si>
   <si>
-    <t>Janiyah Obilex</t>
-  </si>
-  <si>
     <t>Justin Lhance Alto</t>
   </si>
   <si>
@@ -412,6 +397,12 @@
   </si>
   <si>
     <t>Aiden Rhyle</t>
+  </si>
+  <si>
+    <t>Janiyah Ruisse Obiles</t>
+  </si>
+  <si>
+    <t>Richard Obiles</t>
   </si>
 </sst>
 </file>
@@ -608,6 +599,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1006,7 +1001,7 @@
       </c>
       <c r="B3" s="2">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46071</v>
       </c>
       <c r="C3" s="2"/>
     </row>
@@ -1248,7 +1243,7 @@
       </c>
       <c r="O9" t="str" cm="1">
         <f t="array" aca="1" ref="O9" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>92 years, 2 months, 3 days</v>
+        <v>92 years, 2 months, 11 days</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="O11" t="str" cm="1">
         <f t="array" aca="1" ref="O11" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>90 years, 0 months, 28 days</v>
+        <v>90 years, 1 months, 5 days</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1432,7 +1427,7 @@
       </c>
       <c r="O13" t="str" cm="1">
         <f t="array" aca="1" ref="O13" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>85 years, 7 months, 21 days</v>
+        <v>85 years, 7 months, 29 days</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="O15" t="str" cm="1">
         <f t="array" aca="1" ref="O15" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>83 years, 7 months, 9 days</v>
+        <v>83 years, 7 months, 17 days</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -1661,7 +1656,7 @@
       </c>
       <c r="O18" t="str" cm="1">
         <f t="array" aca="1" ref="O18" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>78 years, 2 months, 4 days</v>
+        <v>78 years, 2 months, 12 days</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -1802,7 +1797,7 @@
       </c>
       <c r="O21" t="str" cm="1">
         <f t="array" aca="1" ref="O21" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>71 years, 10 months, 26 days</v>
+        <v>71 years, 11 months, 3 days</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1939,7 +1934,7 @@
       </c>
       <c r="O24" t="str" cm="1">
         <f t="array" aca="1" ref="O24" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>69 years, 4 months, 27 days</v>
+        <v>69 years, 5 months, 4 days</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -2593,7 +2588,7 @@
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" cm="1">
@@ -2623,7 +2618,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
@@ -3204,7 +3199,7 @@
         <v>48</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
@@ -3219,7 +3214,7 @@
         <v>20</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" t="str" cm="1">
@@ -3230,9 +3225,9 @@
         <f t="array" ref="L53">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v/>
       </c>
-      <c r="M53" t="str" cm="1">
+      <c r="M53" cm="1">
         <f t="array" ref="M53">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="N53" t="str" cm="1">
         <f t="array" ref="N53">lambda_lifetimeage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]])</f>
@@ -3249,7 +3244,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
@@ -3264,7 +3259,7 @@
         <v>35</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" cm="1">
@@ -3294,7 +3289,7 @@
         <v>50</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
@@ -3308,9 +3303,7 @@
       <c r="H55" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I55" s="3" t="s">
-        <v>70</v>
-      </c>
+      <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" cm="1">
         <f t="array" ref="K55">_xlfn.XLOOKUP(Family[[#This Row],[Father]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
@@ -3339,7 +3332,7 @@
         <v>51</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
@@ -3384,7 +3377,7 @@
         <v>52</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
@@ -3399,7 +3392,7 @@
         <v>20</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" t="str" cm="1">
@@ -3410,9 +3403,9 @@
         <f t="array" ref="L57">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v/>
       </c>
-      <c r="M57" t="str" cm="1">
+      <c r="M57" cm="1">
         <f t="array" ref="M57">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="N57" t="str" cm="1">
         <f t="array" ref="N57">lambda_lifetimeage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]])</f>
@@ -3429,7 +3422,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
@@ -3444,7 +3437,7 @@
         <v>37</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" cm="1">
@@ -3474,7 +3467,7 @@
         <v>54</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
@@ -3489,7 +3482,7 @@
         <v>37</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" cm="1">
@@ -3519,7 +3512,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3" t="s">
@@ -3534,7 +3527,7 @@
         <v>20</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" t="str" cm="1">
@@ -3564,7 +3557,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
@@ -3579,7 +3572,7 @@
         <v>39</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" cm="1">
@@ -3609,7 +3602,7 @@
         <v>57</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
@@ -3620,7 +3613,7 @@
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
       <c r="I62" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" t="str" cm="1">
@@ -3650,7 +3643,7 @@
         <v>58</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3" t="s">
@@ -3695,7 +3688,7 @@
         <v>59</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3" t="s">
@@ -3740,7 +3733,7 @@
         <v>60</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
@@ -3785,7 +3778,7 @@
         <v>61</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
@@ -3830,7 +3823,7 @@
         <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
@@ -3875,7 +3868,7 @@
         <v>63</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
@@ -3920,7 +3913,7 @@
         <v>64</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
@@ -3965,7 +3958,7 @@
         <v>65</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
@@ -4010,7 +4003,7 @@
         <v>66</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
@@ -4055,7 +4048,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
@@ -4100,7 +4093,7 @@
         <v>68</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
@@ -4145,7 +4138,7 @@
         <v>69</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
@@ -4190,7 +4183,7 @@
         <v>70</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
@@ -4235,7 +4228,7 @@
         <v>71</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
@@ -4280,7 +4273,7 @@
         <v>72</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
@@ -4325,7 +4318,7 @@
         <v>73</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
@@ -4370,7 +4363,7 @@
         <v>74</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
@@ -4379,10 +4372,10 @@
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="3" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>20</v>
@@ -4392,9 +4385,9 @@
         <f t="array" ref="K79">_xlfn.XLOOKUP(Family[[#This Row],[Father]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v>48</v>
       </c>
-      <c r="L79" t="str" cm="1">
+      <c r="L79" cm="1">
         <f t="array" ref="L79">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="M79" t="str" cm="1">
         <f t="array" ref="M79">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
@@ -4415,7 +4408,7 @@
         <v>75</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
@@ -4424,11 +4417,9 @@
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="G80" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H80" s="3"/>
       <c r="I80" s="3" t="s">
         <v>20</v>
       </c>
@@ -4460,7 +4451,7 @@
         <v>76</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
@@ -4469,11 +4460,9 @@
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H81" s="3"/>
       <c r="I81" s="3" t="s">
         <v>20</v>
       </c>
@@ -4505,7 +4494,7 @@
         <v>77</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
@@ -4514,11 +4503,9 @@
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
       <c r="G82" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H82" s="3"/>
       <c r="I82" s="3" t="s">
         <v>20</v>
       </c>
@@ -4550,7 +4537,7 @@
         <v>78</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
@@ -4559,11 +4546,9 @@
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>70</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="H83" s="3"/>
       <c r="I83" s="3" t="s">
         <v>20</v>
       </c>
@@ -4595,7 +4580,7 @@
         <v>79</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
@@ -4607,7 +4592,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>20</v>
@@ -4640,7 +4625,7 @@
         <v>80</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
@@ -4651,10 +4636,10 @@
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>20</v>
@@ -4664,9 +4649,9 @@
         <f t="array" ref="K85">_xlfn.XLOOKUP(Family[[#This Row],[Father]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v>52</v>
       </c>
-      <c r="L85" t="str" cm="1">
+      <c r="L85" cm="1">
         <f t="array" ref="L85">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="M85" t="str" cm="1">
         <f t="array" ref="M85">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
@@ -4678,7 +4663,7 @@
       </c>
       <c r="O85" t="str" cm="1">
         <f t="array" aca="1" ref="O85" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>11 years, 7 months, 14 days</v>
+        <v>11 years, 7 months, 22 days</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
@@ -4687,7 +4672,7 @@
         <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
@@ -4700,10 +4685,10 @@
         <v>45164</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="I86" s="4"/>
       <c r="J86" s="3"/>
@@ -4711,9 +4696,9 @@
         <f t="array" ref="K86">_xlfn.XLOOKUP(Family[[#This Row],[Father]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v>52</v>
       </c>
-      <c r="L86" t="str" cm="1">
+      <c r="L86" cm="1">
         <f t="array" ref="L86">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="M86" t="str" cm="1">
         <f t="array" ref="M86">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
@@ -4734,7 +4719,7 @@
         <v>82</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
@@ -4745,10 +4730,10 @@
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H87" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="I87" s="4"/>
       <c r="J87" s="3"/>
@@ -4756,9 +4741,9 @@
         <f t="array" ref="K87">_xlfn.XLOOKUP(Family[[#This Row],[Father]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
         <v>52</v>
       </c>
-      <c r="L87" t="str" cm="1">
+      <c r="L87" cm="1">
         <f t="array" ref="L87">_xlfn.XLOOKUP(Family[[#This Row],[Mother]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="M87" t="str" cm="1">
         <f t="array" ref="M87">_xlfn.XLOOKUP(Family[[#This Row],[Spouse]],Family[[Name]:[Name]],Family[[PersonID]:[PersonID]],"",0)</f>
@@ -4770,7 +4755,7 @@
       </c>
       <c r="O87" t="str" cm="1">
         <f t="array" aca="1" ref="O87" ca="1">lambda_currentage(Family[[#This Row],[BirthDate]],Family[[#This Row],[DeathDate]],$B$3)</f>
-        <v>2 years, 4 months, 22 days</v>
+        <v>2 years, 4 months, 30 days</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
@@ -4779,7 +4764,7 @@
         <v>83</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
@@ -4788,10 +4773,10 @@
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="G88" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I88" s="4"/>
       <c r="J88" s="3"/>
@@ -5493,12 +5478,15 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D88" xr:uid="{88B235F2-0B48-45BB-976F-4DE8389AF51E}">
       <formula1>INDIRECT("Lookup_Gender[Gender]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I88 J6:J85" xr:uid="{22E5EF5B-D42A-4822-8EC6-9949242216BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J6:J85 G6:I88" xr:uid="{22E5EF5B-D42A-4822-8EC6-9949242216BD}">
       <formula1>INDIRECT("Family[name]")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="I72:I85 H73:H75 G84 G60:H60 G57:H57 G52:H53 G44:H50 G36:H38 G6:H30 G32:H34 I63:I71 I8:I52 I58:I62 I54:I56" listDataValidation="1"/>
+  </ignoredErrors>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -5725,7 +5713,7 @@
       </c>
       <c r="K9" t="str">
         <f ca="1"/>
-        <v>92 years, 2 months, 3 days</v>
+        <v>92 years, 2 months, 11 days</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -5803,7 +5791,7 @@
       </c>
       <c r="K11" t="str">
         <f ca="1"/>
-        <v>90 years, 0 months, 28 days</v>
+        <v>90 years, 1 months, 5 days</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -5881,7 +5869,7 @@
       </c>
       <c r="K13" t="str">
         <f ca="1"/>
-        <v>85 years, 7 months, 21 days</v>
+        <v>85 years, 7 months, 29 days</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -5959,7 +5947,7 @@
       </c>
       <c r="K15" t="str">
         <f ca="1"/>
-        <v>83 years, 7 months, 9 days</v>
+        <v>83 years, 7 months, 17 days</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -6076,7 +6064,7 @@
       </c>
       <c r="K18" t="str">
         <f ca="1"/>
-        <v>78 years, 2 months, 4 days</v>
+        <v>78 years, 2 months, 12 days</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -6193,7 +6181,7 @@
       </c>
       <c r="K21" t="str">
         <f ca="1"/>
-        <v>71 years, 10 months, 26 days</v>
+        <v>71 years, 11 months, 3 days</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -6310,7 +6298,7 @@
       </c>
       <c r="K24" t="str">
         <f ca="1"/>
-        <v>69 years, 4 months, 27 days</v>
+        <v>69 years, 5 months, 4 days</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -7413,7 +7401,7 @@
         <v>48</v>
       </c>
       <c r="B53" t="str">
-        <v>Richard Obilex</v>
+        <v>Richard Obiles</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -7433,8 +7421,8 @@
       <c r="H53" t="str">
         <v/>
       </c>
-      <c r="I53" t="str">
-        <v/>
+      <c r="I53">
+        <v>49</v>
       </c>
       <c r="J53" t="str">
         <v/>
@@ -7589,8 +7577,8 @@
       <c r="H57" t="str">
         <v/>
       </c>
-      <c r="I57" t="str">
-        <v/>
+      <c r="I57">
+        <v>53</v>
       </c>
       <c r="J57" t="str">
         <v/>
@@ -8427,7 +8415,7 @@
         <v>74</v>
       </c>
       <c r="B79" t="str">
-        <v>Janiyah Obilex</v>
+        <v>Janiyah Ruisse Obiles</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -8444,8 +8432,8 @@
       <c r="G79">
         <v>48</v>
       </c>
-      <c r="H79" t="str">
-        <v/>
+      <c r="H79">
+        <v>49</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -8678,8 +8666,8 @@
       <c r="G85">
         <v>52</v>
       </c>
-      <c r="H85" t="str">
-        <v/>
+      <c r="H85">
+        <v>53</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -8689,7 +8677,7 @@
       </c>
       <c r="K85" t="str">
         <f ca="1"/>
-        <v>11 years, 7 months, 14 days</v>
+        <v>11 years, 7 months, 22 days</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -8717,8 +8705,8 @@
       <c r="G86">
         <v>52</v>
       </c>
-      <c r="H86" t="str">
-        <v/>
+      <c r="H86">
+        <v>53</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -8756,8 +8744,8 @@
       <c r="G87">
         <v>52</v>
       </c>
-      <c r="H87" t="str">
-        <v/>
+      <c r="H87">
+        <v>53</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -8767,7 +8755,7 @@
       </c>
       <c r="K87" t="str">
         <f ca="1"/>
-        <v>2 years, 4 months, 22 days</v>
+        <v>2 years, 4 months, 30 days</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -8836,7 +8824,7 @@
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -8844,7 +8832,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
